--- a/data/trans_dic/P1001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,53</t>
+          <t>2,76; 6,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,04</t>
+          <t>2,46; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,4</t>
+          <t>3,04; 7,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,75</t>
+          <t>3,74; 8,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,04</t>
+          <t>4,38; 10,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,85</t>
+          <t>4,6; 11,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,23</t>
+          <t>4,46; 10,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,93</t>
+          <t>5,36; 9,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,11</t>
+          <t>3,85; 7,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,78</t>
+          <t>3,94; 7,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,6</t>
+          <t>4,15; 7,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,58</t>
+          <t>4,99; 8,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,99</t>
+          <t>2,58; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,83</t>
+          <t>4,46; 10,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,85</t>
+          <t>3,13; 7,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,65</t>
+          <t>1,49; 4,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,78</t>
+          <t>5,86; 11,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,03</t>
+          <t>6,19; 12,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,35</t>
+          <t>4,16; 9,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,52</t>
+          <t>6,84; 12,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,59</t>
+          <t>4,68; 8,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,67</t>
+          <t>5,67; 9,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,63</t>
+          <t>4,12; 8,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,45</t>
+          <t>4,28; 7,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,63</t>
+          <t>4,44; 8,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,32</t>
+          <t>6,28; 11,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,73</t>
+          <t>4,95; 9,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,93</t>
+          <t>1,79; 9,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 16,6</t>
+          <t>7,12; 17,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 23,47</t>
+          <t>13,75; 23,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,02</t>
+          <t>8,69; 20,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,29</t>
+          <t>7,65; 15,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,61</t>
+          <t>5,62; 9,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,01</t>
+          <t>9,21; 13,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,82</t>
+          <t>6,49; 11,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,67</t>
+          <t>2,73; 9,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,13</t>
+          <t>6,32; 9,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,93</t>
+          <t>7,37; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,34</t>
+          <t>4,57; 7,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,19</t>
+          <t>5,08; 8,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,16</t>
+          <t>7,45; 11,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,15</t>
+          <t>9,93; 14,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,31</t>
+          <t>9,81; 14,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 9,17</t>
+          <t>3,65; 9,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,71</t>
+          <t>7,19; 9,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,88</t>
+          <t>8,87; 11,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,68</t>
+          <t>7,2; 9,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,88</t>
+          <t>4,59; 7,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,44</t>
+          <t>3,88; 9,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,01</t>
+          <t>3,76; 8,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,91</t>
+          <t>6,45; 10,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,18</t>
+          <t>6,25; 11,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,63</t>
+          <t>7,29; 12,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 22,81</t>
+          <t>16,99; 23,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,35</t>
+          <t>14,09; 19,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,96</t>
+          <t>10,11; 16,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,45</t>
+          <t>6,59; 10,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,19; 16,27</t>
+          <t>12,37; 16,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 14,88</t>
+          <t>11,13; 15,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,6</t>
+          <t>9,44; 13,6</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,27</t>
+          <t>1,91; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,02</t>
+          <t>1,81; 6,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,67</t>
+          <t>1,91; 6,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,73</t>
+          <t>1,58; 9,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,68</t>
+          <t>7,96; 11,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 17,83</t>
+          <t>13,58; 17,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,4</t>
+          <t>10,89; 15,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 17,61</t>
+          <t>13,11; 18,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,09</t>
+          <t>7,15; 9,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,49; 15,18</t>
+          <t>11,43; 15,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 12,96</t>
+          <t>9,31; 12,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,63</t>
+          <t>10,63; 14,62</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,95</t>
+          <t>5,25; 6,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 7,96</t>
+          <t>6,21; 8,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,0</t>
+          <t>5,22; 7,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,66</t>
+          <t>4,29; 6,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,43</t>
+          <t>8,49; 10,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,4; 15,87</t>
+          <t>13,53; 15,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,05; 13,38</t>
+          <t>11,14; 13,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,85</t>
+          <t>8,73; 11,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,42</t>
+          <t>7,15; 8,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,18; 11,63</t>
+          <t>10,16; 11,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 9,95</t>
+          <t>8,48; 9,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,05</t>
+          <t>7,13; 9,05</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12198; 30940</t>
+          <t>13074; 31456</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11339; 30718</t>
+          <t>10739; 29620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12346; 31770</t>
+          <t>13065; 32176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19171; 44228</t>
+          <t>18893; 43804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12980; 30797</t>
+          <t>13447; 30858</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15191; 34107</t>
+          <t>14451; 34800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15714; 35514</t>
+          <t>15479; 34855</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24662; 44455</t>
+          <t>23976; 43581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29350; 55471</t>
+          <t>30018; 55516</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30603; 58395</t>
+          <t>29572; 56562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33601; 58991</t>
+          <t>32205; 59862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48544; 81775</t>
+          <t>47528; 78710</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9139; 25656</t>
+          <t>9474; 26445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17432; 41154</t>
+          <t>18692; 41938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11302; 29618</t>
+          <t>11799; 28824</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6541; 21048</t>
+          <t>6752; 20430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21936; 43817</t>
+          <t>21775; 43064</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20442; 44033</t>
+          <t>20938; 43422</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14756; 34826</t>
+          <t>15471; 36439</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26456; 47908</t>
+          <t>26156; 46354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34985; 63438</t>
+          <t>34550; 62108</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42155; 73207</t>
+          <t>42931; 73099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30092; 57186</t>
+          <t>30898; 60419</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36147; 62195</t>
+          <t>35689; 61451</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24423; 46798</t>
+          <t>24064; 46234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40007; 71247</t>
+          <t>39553; 70731</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26055; 50770</t>
+          <t>25852; 49223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10281; 59679</t>
+          <t>11945; 61721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11409; 27853</t>
+          <t>11943; 28558</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35106; 61054</t>
+          <t>35764; 61219</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14241; 33261</t>
+          <t>14430; 34434</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13026; 25513</t>
+          <t>12772; 25394</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38386; 68224</t>
+          <t>39920; 66705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82250; 124581</t>
+          <t>81917; 121799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45773; 74461</t>
+          <t>44660; 75936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21330; 80756</t>
+          <t>22832; 80667</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77125; 113106</t>
+          <t>78266; 116088</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85473; 126722</t>
+          <t>85428; 127164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52232; 84353</t>
+          <t>52579; 84693</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53638; 84644</t>
+          <t>52512; 83380</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55345; 86881</t>
+          <t>53179; 85136</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77275; 116182</t>
+          <t>76133; 114327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79185; 118187</t>
+          <t>80996; 118702</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37432; 89556</t>
+          <t>35666; 90400</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142438; 189540</t>
+          <t>140323; 188045</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170059; 228826</t>
+          <t>170750; 228417</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>139863; 191272</t>
+          <t>142214; 189236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94828; 158442</t>
+          <t>92206; 159235</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13854; 33101</t>
+          <t>13609; 32178</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19247; 40825</t>
+          <t>19142; 40941</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39248; 67694</t>
+          <t>40051; 67423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29426; 53118</t>
+          <t>29713; 52519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43378; 71844</t>
+          <t>41441; 70328</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>128951; 173249</t>
+          <t>129036; 175414</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>103347; 142843</t>
+          <t>104007; 145909</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81456; 134156</t>
+          <t>85008; 136797</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60147; 96024</t>
+          <t>60605; 96219</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154756; 206502</t>
+          <t>156990; 210670</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149070; 202181</t>
+          <t>151259; 205677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124892; 178925</t>
+          <t>124255; 178924</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5830; 18705</t>
+          <t>5688; 19383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4886; 18736</t>
+          <t>4820; 18039</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5175; 19139</t>
+          <t>5493; 18934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3997; 23393</t>
+          <t>3794; 23052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>102590; 145813</t>
+          <t>99427; 141364</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>151316; 197755</t>
+          <t>150615; 197665</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>119942; 166642</t>
+          <t>117850; 165706</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100021; 133904</t>
+          <t>99738; 137096</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111575; 156158</t>
+          <t>110534; 154325</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>158193; 208856</t>
+          <t>157293; 206974</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128306; 177445</t>
+          <t>127484; 176621</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>107098; 146485</t>
+          <t>106376; 146343</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>172708; 227186</t>
+          <t>171777; 227853</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>207853; 272174</t>
+          <t>212293; 276493</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>179466; 237155</t>
+          <t>176700; 237834</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151303; 224662</t>
+          <t>144787; 220855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>283907; 352337</t>
+          <t>286896; 356246</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>475477; 563019</t>
+          <t>480016; 566644</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>390309; 472640</t>
+          <t>393378; 473080</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>303002; 423596</t>
+          <t>311978; 424553</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>472093; 559457</t>
+          <t>475504; 559871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>709191; 810407</t>
+          <t>707644; 816482</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>588485; 688510</t>
+          <t>586610; 690946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>487237; 629008</t>
+          <t>495547; 629145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,64</t>
+          <t>2,69; 6,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,79</t>
+          <t>2,52; 6,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,5</t>
+          <t>3,04; 7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,67</t>
+          <t>3,4; 7,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,06</t>
+          <t>4,53; 9,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,07</t>
+          <t>4,77; 11,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,04</t>
+          <t>4,32; 10,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,74</t>
+          <t>5,77; 10,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,11</t>
+          <t>3,85; 6,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,53</t>
+          <t>4,0; 7,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,71</t>
+          <t>4,2; 7,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,26</t>
+          <t>5,0; 8,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,21</t>
+          <t>2,3; 7,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,01</t>
+          <t>3,94; 9,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,64</t>
+          <t>3,19; 8,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,52</t>
+          <t>1,61; 4,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,58</t>
+          <t>5,96; 11,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,85</t>
+          <t>6,05; 12,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,79</t>
+          <t>4,06; 9,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,12</t>
+          <t>7,32; 12,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,41</t>
+          <t>4,7; 8,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,66</t>
+          <t>5,64; 10,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,06</t>
+          <t>4,16; 7,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,36</t>
+          <t>4,61; 7,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,52</t>
+          <t>4,25; 8,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,24</t>
+          <t>6,16; 10,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,43</t>
+          <t>4,8; 9,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,24</t>
+          <t>5,18; 10,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 17,02</t>
+          <t>6,53; 16,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 23,53</t>
+          <t>13,2; 23,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 20,73</t>
+          <t>8,38; 20,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,21</t>
+          <t>7,6; 14,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,39</t>
+          <t>5,67; 9,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,69</t>
+          <t>9,1; 13,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,04</t>
+          <t>6,61; 11,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,66</t>
+          <t>6,76; 10,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,37</t>
+          <t>6,21; 9,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,97</t>
+          <t>7,23; 10,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,37</t>
+          <t>4,65; 7,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,07</t>
+          <t>5,21; 7,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,92</t>
+          <t>7,64; 12,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,91</t>
+          <t>10,01; 14,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,37</t>
+          <t>9,42; 14,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,25</t>
+          <t>7,08; 10,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,63</t>
+          <t>7,24; 9,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,86</t>
+          <t>8,92; 11,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,58</t>
+          <t>7,27; 9,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,92</t>
+          <t>6,49; 8,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,18</t>
+          <t>3,91; 9,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,03</t>
+          <t>3,8; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,86</t>
+          <t>6,47; 10,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,06</t>
+          <t>5,54; 9,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,37</t>
+          <t>7,55; 12,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 23,1</t>
+          <t>17,47; 23,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 19,76</t>
+          <t>13,98; 19,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 16,27</t>
+          <t>12,88; 17,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,47</t>
+          <t>6,63; 10,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,6</t>
+          <t>12,57; 16,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,13; 15,14</t>
+          <t>11,11; 14,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,6</t>
+          <t>10,2; 13,2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,5</t>
+          <t>1,82; 6,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,76</t>
+          <t>1,8; 6,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,59</t>
+          <t>1,92; 6,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,58</t>
+          <t>2,07; 10,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,32</t>
+          <t>8,07; 11,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,82</t>
+          <t>13,52; 18,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,31</t>
+          <t>11,01; 15,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,11; 18,03</t>
+          <t>12,82; 17,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,98</t>
+          <t>7,12; 10,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,43; 15,04</t>
+          <t>11,56; 15,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,9</t>
+          <t>9,37; 12,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 14,62</t>
+          <t>10,86; 14,97</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,97</t>
+          <t>5,23; 6,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 8,08</t>
+          <t>6,19; 7,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,02</t>
+          <t>5,26; 7,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,54</t>
+          <t>5,24; 6,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 10,55</t>
+          <t>8,34; 10,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,53; 15,97</t>
+          <t>13,5; 15,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14; 13,4</t>
+          <t>11,16; 13,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,87</t>
+          <t>10,66; 12,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,42</t>
+          <t>7,11; 8,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,72</t>
+          <t>10,12; 11,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,99</t>
+          <t>8,53; 10,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,05</t>
+          <t>8,17; 9,45</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>66196</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13074; 31456</t>
+          <t>12736; 31771</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10739; 29620</t>
+          <t>10995; 29939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13065; 32176</t>
+          <t>13056; 31390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18893; 43804</t>
+          <t>18726; 43108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13447; 30858</t>
+          <t>13903; 30453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14451; 34800</t>
+          <t>15003; 35104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15479; 34855</t>
+          <t>14984; 34747</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23976; 43581</t>
+          <t>28197; 49855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30018; 55516</t>
+          <t>30016; 54477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29572; 56562</t>
+          <t>29993; 56256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32205; 59862</t>
+          <t>32611; 58874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47528; 78710</t>
+          <t>51940; 84855</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47218</t>
+          <t>54235</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9474; 26445</t>
+          <t>8453; 26324</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18692; 41938</t>
+          <t>16516; 39996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11799; 28824</t>
+          <t>12019; 30603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6752; 20430</t>
+          <t>7798; 23073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21775; 43064</t>
+          <t>22166; 44037</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20938; 43422</t>
+          <t>20438; 42378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15471; 36439</t>
+          <t>15125; 36369</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26156; 46354</t>
+          <t>30963; 53212</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34550; 62108</t>
+          <t>34694; 61794</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42931; 73099</t>
+          <t>42696; 76497</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30898; 60419</t>
+          <t>31166; 58813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35689; 61451</t>
+          <t>41749; 68386</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>55949</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24064; 46234</t>
+          <t>23069; 45391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39553; 70731</t>
+          <t>38802; 69046</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25852; 49223</t>
+          <t>25076; 49001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11945; 61721</t>
+          <t>24423; 49985</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11943; 28558</t>
+          <t>10963; 27927</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35764; 61219</t>
+          <t>34345; 60718</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14430; 34434</t>
+          <t>13928; 34828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12772; 25394</t>
+          <t>14246; 27743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39920; 66705</t>
+          <t>40251; 68746</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81917; 121799</t>
+          <t>80946; 122832</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44660; 75936</t>
+          <t>45495; 77283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22832; 80667</t>
+          <t>44555; 71062</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67008</t>
+          <t>73683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67070</t>
+          <t>74662</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>148345</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78266; 116088</t>
+          <t>76930; 114800</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85428; 127164</t>
+          <t>83774; 123802</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52579; 84693</t>
+          <t>53424; 86602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52512; 83380</t>
+          <t>58923; 90141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53179; 85136</t>
+          <t>54557; 85787</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76133; 114327</t>
+          <t>76770; 113803</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80996; 118702</t>
+          <t>77825; 116495</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35666; 90400</t>
+          <t>60924; 89116</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>140323; 188045</t>
+          <t>141369; 191853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170750; 228417</t>
+          <t>171834; 230918</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142214; 189236</t>
+          <t>143647; 191285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>92206; 159235</t>
+          <t>129146; 171813</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39610</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>112701</t>
+          <t>121803</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>152311</t>
+          <t>164008</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13609; 32178</t>
+          <t>13714; 33225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19142; 40941</t>
+          <t>19362; 41658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40051; 67423</t>
+          <t>40184; 68008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29713; 52519</t>
+          <t>31486; 56597</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41441; 70328</t>
+          <t>42962; 71331</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>129036; 175414</t>
+          <t>132705; 175919</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>104007; 145909</t>
+          <t>103170; 144966</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85008; 136797</t>
+          <t>106939; 141133</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60605; 96219</t>
+          <t>60905; 98499</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156990; 210670</t>
+          <t>159535; 209053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151259; 205677</t>
+          <t>150932; 199603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124255; 178924</t>
+          <t>142677; 184509</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>115987</t>
+          <t>125763</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>125143</t>
+          <t>136460</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5688; 19383</t>
+          <t>5418; 19341</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4820; 18039</t>
+          <t>4803; 17658</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5493; 18934</t>
+          <t>5509; 19742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3794; 23052</t>
+          <t>4903; 24197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99427; 141364</t>
+          <t>100788; 142162</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>150615; 197665</t>
+          <t>150033; 200120</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>117850; 165706</t>
+          <t>119128; 165937</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99738; 137096</t>
+          <t>108098; 146015</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110534; 154325</t>
+          <t>110126; 156320</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>157293; 206974</t>
+          <t>159066; 208567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>127484; 176621</t>
+          <t>128349; 177013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>106376; 146343</t>
+          <t>117387; 161803</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190636</t>
+          <t>204511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>382283</t>
+          <t>420683</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>572919</t>
+          <t>625194</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>171777; 227853</t>
+          <t>171066; 225922</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>212293; 276493</t>
+          <t>211748; 273407</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176700; 237834</t>
+          <t>178125; 236890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144787; 220855</t>
+          <t>180278; 236629</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>286896; 356246</t>
+          <t>281833; 352274</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>480016; 566644</t>
+          <t>479102; 565452</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>393378; 473080</t>
+          <t>394045; 476814</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>311978; 424553</t>
+          <t>387174; 454791</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>475504; 559871</t>
+          <t>472935; 564735</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>707644; 816482</t>
+          <t>705372; 812996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>586610; 690946</t>
+          <t>590219; 693200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>495547; 629145</t>
+          <t>578299; 668383</t>
         </is>
       </c>
     </row>
